--- a/docs/students/8o..xlsx
+++ b/docs/students/8o..xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\María Alexandra\Listados Actualizados\LISTADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\AgenteIA_Alexandra\docs\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD8F83C-5895-4AD1-98D0-126CD018C0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05822E75-83EE-4415-827A-7F23D3E0D9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="200">
   <si>
     <t>#</t>
   </si>
@@ -88,21 +88,6 @@
     <t>luzmilacarvajal23@gmail.com</t>
   </si>
   <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Correo institucional</t>
-  </si>
-  <si>
-    <t>Nombre mamá</t>
-  </si>
-  <si>
-    <t>Nombre papá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORREO PAPÁ </t>
-  </si>
-  <si>
     <t>Eighth</t>
   </si>
   <si>
@@ -653,6 +638,30 @@
   </si>
   <si>
     <t>23AC0265@cac.edu.co</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>CORREO INSTITUCIONAL</t>
+  </si>
+  <si>
+    <t>NOMBRE MAMÁ</t>
+  </si>
+  <si>
+    <t>NOMBRE  PAPÁ</t>
+  </si>
+  <si>
+    <t>CORREO PAPÁ</t>
+  </si>
+  <si>
+    <t>23AC0250@cac.edu.co</t>
+  </si>
+  <si>
+    <t>ID_DRIVE</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -687,7 +696,7 @@
       <sz val="12"/>
       <color rgb="FF242424"/>
       <name val="Segoe UI"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -710,7 +719,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -757,6 +766,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -781,20 +810,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1136,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="5" max="5" width="36.625" customWidth="1"/>
@@ -1144,11 +1177,12 @@
     <col min="7" max="7" width="31.75" customWidth="1"/>
     <col min="8" max="8" width="35.375" customWidth="1"/>
     <col min="9" max="9" width="30.375" customWidth="1"/>
-    <col min="10" max="10" width="38.875" customWidth="1"/>
+    <col min="10" max="10" width="36.5" customWidth="1"/>
+    <col min="11" max="11" width="78.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:14" ht="15">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -1160,921 +1194,1016 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="I1" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="K5" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="F6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="H6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="I6" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="J6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1">
+      <c r="K6" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="H7" s="9"/>
       <c r="I7" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>42</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="I9" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="J9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="8"/>
       <c r="I14" s="1"/>
       <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10">
+        <v>84</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>187</v>
+        <v>107</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>182</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>109</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>189</v>
+        <v>123</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>127</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>190</v>
+        <v>128</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="K27" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="K29" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="12">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="F30" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="14">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="14"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2096,7 +2225,7 @@
     <hyperlink ref="J19" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
     <hyperlink ref="F20" r:id="rId17" display="25AC0569@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
     <hyperlink ref="J20" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
-    <hyperlink ref="F23" r:id="rId19" display="23AC0236@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
+    <hyperlink ref="F23" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
     <hyperlink ref="H23" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
     <hyperlink ref="J23" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
     <hyperlink ref="F24" r:id="rId22" display="23AC0264@australianocampestre.edu.co" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
@@ -2149,13 +2278,24 @@
     <hyperlink ref="H30" r:id="rId69" xr:uid="{00000000-0004-0000-0200-000044000000}"/>
     <hyperlink ref="H18" r:id="rId70" xr:uid="{00000000-0004-0000-0200-000045000000}"/>
     <hyperlink ref="J18" r:id="rId71" xr:uid="{00000000-0004-0000-0200-000046000000}"/>
+    <hyperlink ref="K2" r:id="rId72" xr:uid="{B9192177-C027-4280-A345-9531C8A3F34B}"/>
+    <hyperlink ref="K3:K18" r:id="rId73" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{1A782808-419B-41DC-B073-0BA6982F51DE}"/>
+    <hyperlink ref="K20" r:id="rId74" xr:uid="{219150BE-6989-444C-BB5A-5BDDDF067C1D}"/>
+    <hyperlink ref="K21:K30" r:id="rId75" display="https://drive.google.com/drive/folders/1odLpbR5jpl2Qf17hE0nwNbIF1OdTgv3o?usp=drive_link" xr:uid="{91796CC7-55E5-4B2B-BA63-8773F6F2376A}"/>
+    <hyperlink ref="K19" r:id="rId76" xr:uid="{FDFEF81C-A11F-48F3-B533-AF7B276D3690}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId72"/>
+  <legacyDrawing r:id="rId77"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010033786E0F47F2E4479E1418699C7D1887" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8889b9d8e9583677ca2221be300ac5d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b44af97c-a663-43df-bc64-dfb44812992d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8c5274dc35b9ea6c79ecd381a4eab1a6" ns2:_="">
     <xsd:import namespace="b44af97c-a663-43df-bc64-dfb44812992d"/>
@@ -2293,7 +2433,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2302,13 +2442,16 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35073413-9516-4B73-8842-99BBF230AC45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{196073E8-6B75-4A3D-94ED-1A629E1F09BE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2326,19 +2469,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBBEA71-C632-4AE8-B7C8-3F289DADFCB3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35073413-9516-4B73-8842-99BBF230AC45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>